--- a/data/trans_orig/P36B07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B07-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de zumo natural de frutas o verduras en 2016</t>
+          <t>Población según la frecuencia de consumo de zumo natural de frutas o verduras en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62738</t>
+          <t>63200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95164</t>
+          <t>95466</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35585</t>
+          <t>34952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61377</t>
+          <t>61197</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105166</t>
+          <t>106545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148499</t>
+          <t>147402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50111</t>
+          <t>50292</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80592</t>
+          <t>81280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43945</t>
+          <t>46559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73697</t>
+          <t>74357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100839</t>
+          <t>104398</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144433</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93354</t>
+          <t>93451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132012</t>
+          <t>130613</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66196</t>
+          <t>66214</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>97496</t>
+          <t>98306</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>164929</t>
+          <t>169149</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>216743</t>
+          <t>213932</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>27,75%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64106</t>
+          <t>61949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97457</t>
+          <t>97921</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56972</t>
+          <t>55969</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87953</t>
+          <t>86599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128611</t>
+          <t>129391</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>173531</t>
+          <t>174483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78389</t>
+          <t>78221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>113667</t>
+          <t>113417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70032</t>
+          <t>71600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104279</t>
+          <t>106204</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>159447</t>
+          <t>157788</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>207432</t>
+          <t>207131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61146</t>
+          <t>62714</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95774</t>
+          <t>94607</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46702</t>
+          <t>48061</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74984</t>
+          <t>77408</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118818</t>
+          <t>117436</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161374</t>
+          <t>158865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68290</t>
+          <t>66621</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102087</t>
+          <t>98646</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59948</t>
+          <t>60714</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92903</t>
+          <t>90537</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136029</t>
+          <t>136947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>181162</t>
+          <t>182103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70648</t>
+          <t>71413</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>104581</t>
+          <t>105033</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76560</t>
+          <t>75956</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110412</t>
+          <t>109733</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>155993</t>
+          <t>155370</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>205097</t>
+          <t>203052</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44479</t>
+          <t>47084</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74538</t>
+          <t>75202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49323</t>
+          <t>49767</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78086</t>
+          <t>77530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103549</t>
+          <t>103829</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143515</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54007</t>
+          <t>52928</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84271</t>
+          <t>84462</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62117</t>
+          <t>62609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92477</t>
+          <t>93733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123143</t>
+          <t>122696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168219</t>
+          <t>168077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118567</t>
+          <t>119033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161996</t>
+          <t>160364</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23807</t>
+          <t>23730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45443</t>
+          <t>45717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148892</t>
+          <t>149267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>195131</t>
+          <t>196055</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86996</t>
+          <t>86913</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>123115</t>
+          <t>121981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38285</t>
+          <t>38630</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>112629</t>
+          <t>111425</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>153267</t>
+          <t>154375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79672</t>
+          <t>79664</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114723</t>
+          <t>115307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28508</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50841</t>
+          <t>51076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>114064</t>
+          <t>113045</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>156443</t>
+          <t>153895</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76098</t>
+          <t>76340</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113402</t>
+          <t>111977</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25714</t>
+          <t>25675</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47355</t>
+          <t>46924</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106963</t>
+          <t>110258</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151071</t>
+          <t>150818</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67481</t>
+          <t>67071</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101919</t>
+          <t>99040</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19524</t>
+          <t>19029</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39684</t>
+          <t>38831</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92260</t>
+          <t>92341</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>131993</t>
+          <t>131680</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>267236</t>
+          <t>267552</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>327076</t>
+          <t>327124</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169776</t>
+          <t>171208</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>220467</t>
+          <t>219574</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>453792</t>
+          <t>457300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>529715</t>
+          <t>531567</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>204692</t>
+          <t>202173</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258276</t>
+          <t>258364</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>101142</t>
+          <t>100764</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>141871</t>
+          <t>141565</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>316138</t>
+          <t>318306</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>382508</t>
+          <t>386435</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>207032</t>
+          <t>209830</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>262750</t>
+          <t>268771</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>153216</t>
+          <t>153703</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>204356</t>
+          <t>204159</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>375957</t>
+          <t>376575</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>450753</t>
+          <t>445409</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>187458</t>
+          <t>190595</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>239493</t>
+          <t>244271</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>132937</t>
+          <t>134056</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>179520</t>
+          <t>179960</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>336857</t>
+          <t>340661</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>408393</t>
+          <t>403557</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145221</t>
+          <t>144736</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>195589</t>
+          <t>192921</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>150093</t>
+          <t>149902</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>200022</t>
+          <t>197320</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>309348</t>
+          <t>311577</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>376337</t>
+          <t>380429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>158438</t>
+          <t>158201</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>205159</t>
+          <t>203399</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>175521</t>
+          <t>173928</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>226451</t>
+          <t>220913</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>346692</t>
+          <t>342954</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>412682</t>
+          <t>410118</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>98532</t>
+          <t>98431</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138660</t>
+          <t>138836</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>125114</t>
+          <t>124082</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>168233</t>
+          <t>167501</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>235118</t>
+          <t>232687</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>296050</t>
+          <t>291644</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105972</t>
+          <t>106494</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>145587</t>
+          <t>145547</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>131371</t>
+          <t>129506</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>174233</t>
+          <t>172997</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>247355</t>
+          <t>246826</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>304109</t>
+          <t>304565</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>81740</t>
+          <t>83566</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>119437</t>
+          <t>119901</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>124159</t>
+          <t>124642</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>169306</t>
+          <t>166754</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>215930</t>
+          <t>219765</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>276314</t>
+          <t>276960</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>68768</t>
+          <t>67859</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>102430</t>
+          <t>102282</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>77808</t>
+          <t>76526</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>115377</t>
+          <t>116379</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>156492</t>
+          <t>156052</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>208459</t>
+          <t>206542</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>38797</t>
+          <t>39091</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>66361</t>
+          <t>64416</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>271152</t>
+          <t>273430</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>331153</t>
+          <t>329343</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>317968</t>
+          <t>316853</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>383079</t>
+          <t>384913</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24547</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>47832</t>
+          <t>48313</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>186172</t>
+          <t>184484</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>236171</t>
+          <t>240184</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>216135</t>
+          <t>219079</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>275359</t>
+          <t>276317</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>55512</t>
+          <t>54261</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>84494</t>
+          <t>84310</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>177340</t>
+          <t>178710</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>229673</t>
+          <t>230258</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>241373</t>
+          <t>243350</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>301233</t>
+          <t>304655</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>47586</t>
+          <t>47748</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>75894</t>
+          <t>74616</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>139864</t>
+          <t>141458</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>188197</t>
+          <t>190580</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>198091</t>
+          <t>200001</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>256410</t>
+          <t>256929</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>57175</t>
+          <t>58051</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>88063</t>
+          <t>87575</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>170541</t>
+          <t>170166</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>224922</t>
+          <t>224214</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>235525</t>
+          <t>235707</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>295075</t>
+          <t>297226</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>770665</t>
+          <t>775856</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>874625</t>
+          <t>872103</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>783304</t>
+          <t>780431</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>892467</t>
+          <t>888398</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1592432</t>
+          <t>1583433</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1735294</t>
+          <t>1727739</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>593056</t>
+          <t>588740</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>683208</t>
+          <t>680113</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>594265</t>
+          <t>593105</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>690325</t>
+          <t>687970</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1213712</t>
+          <t>1210621</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1339231</t>
+          <t>1338648</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>675023</t>
+          <t>669225</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>771842</t>
+          <t>769346</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>694576</t>
+          <t>691730</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>794231</t>
+          <t>789695</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1392494</t>
+          <t>1394234</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1536096</t>
+          <t>1537026</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>563796</t>
+          <t>563612</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>653808</t>
+          <t>650953</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>591556</t>
+          <t>590375</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>684721</t>
+          <t>684407</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1176394</t>
+          <t>1177607</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1308638</t>
+          <t>1312132</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>523051</t>
+          <t>527093</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>611850</t>
+          <t>618967</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>606913</t>
+          <t>607269</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>703382</t>
+          <t>702516</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1157575</t>
+          <t>1161044</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1289803</t>
+          <t>1289409</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B07-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>63200</t>
+          <t>63099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>95466</t>
+          <t>97778</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34952</t>
+          <t>35217</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61197</t>
+          <t>60290</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106545</t>
+          <t>104236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147402</t>
+          <t>144798</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50292</t>
+          <t>49471</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81280</t>
+          <t>78954</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46559</t>
+          <t>45007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74357</t>
+          <t>74243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104398</t>
+          <t>101461</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147140</t>
+          <t>146103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93451</t>
+          <t>94685</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130613</t>
+          <t>130097</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66214</t>
+          <t>65411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>98306</t>
+          <t>97386</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>169149</t>
+          <t>167359</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>213932</t>
+          <t>217024</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,15%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61949</t>
+          <t>63334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97921</t>
+          <t>96671</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55969</t>
+          <t>56914</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86599</t>
+          <t>85913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129391</t>
+          <t>129329</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174483</t>
+          <t>173208</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78221</t>
+          <t>77771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>113417</t>
+          <t>113116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71600</t>
+          <t>72029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>106204</t>
+          <t>104205</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157788</t>
+          <t>159841</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>207131</t>
+          <t>208491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,04%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62714</t>
+          <t>63076</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94607</t>
+          <t>95967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48061</t>
+          <t>47494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77408</t>
+          <t>77248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117436</t>
+          <t>118581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158865</t>
+          <t>161990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66621</t>
+          <t>67801</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98646</t>
+          <t>101170</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60714</t>
+          <t>59811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90537</t>
+          <t>91498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136947</t>
+          <t>137259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>182103</t>
+          <t>182703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71413</t>
+          <t>70526</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105033</t>
+          <t>104928</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75956</t>
+          <t>76313</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>109733</t>
+          <t>109337</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>155370</t>
+          <t>158838</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>203052</t>
+          <t>203736</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47084</t>
+          <t>46030</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75202</t>
+          <t>75333</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49767</t>
+          <t>49288</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77530</t>
+          <t>79065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103829</t>
+          <t>101786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>147140</t>
+          <t>145322</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52928</t>
+          <t>53507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>84462</t>
+          <t>85211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62609</t>
+          <t>61190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>93733</t>
+          <t>93037</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122696</t>
+          <t>125303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168077</t>
+          <t>166101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119033</t>
+          <t>119891</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>160364</t>
+          <t>160311</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23730</t>
+          <t>24851</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45717</t>
+          <t>46442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149267</t>
+          <t>150703</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196055</t>
+          <t>195184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86913</t>
+          <t>87371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121981</t>
+          <t>126382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38630</t>
+          <t>38701</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111425</t>
+          <t>112918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>154375</t>
+          <t>156317</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>79664</t>
+          <t>76567</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>115307</t>
+          <t>113459</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27514</t>
+          <t>27649</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51076</t>
+          <t>50959</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>113045</t>
+          <t>112373</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>153895</t>
+          <t>157440</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76340</t>
+          <t>76625</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>111977</t>
+          <t>109164</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>26757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>49350</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110258</t>
+          <t>108138</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150818</t>
+          <t>149367</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67071</t>
+          <t>66894</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99040</t>
+          <t>100339</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>18820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38831</t>
+          <t>39363</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92341</t>
+          <t>93443</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>131680</t>
+          <t>130616</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>267552</t>
+          <t>269096</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>327124</t>
+          <t>329624</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>171208</t>
+          <t>169917</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>219574</t>
+          <t>220097</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>457300</t>
+          <t>453957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>531567</t>
+          <t>531537</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>202173</t>
+          <t>203618</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258364</t>
+          <t>260566</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100764</t>
+          <t>100299</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>141565</t>
+          <t>139880</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>318306</t>
+          <t>318366</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>386435</t>
+          <t>387727</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>209830</t>
+          <t>206485</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>268771</t>
+          <t>262703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>153703</t>
+          <t>154926</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>204159</t>
+          <t>200510</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>376575</t>
+          <t>375748</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>445409</t>
+          <t>449789</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>190595</t>
+          <t>189154</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>244271</t>
+          <t>243439</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134056</t>
+          <t>134386</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>179960</t>
+          <t>179470</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>340661</t>
+          <t>337231</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>403557</t>
+          <t>405929</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>144736</t>
+          <t>147683</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>192921</t>
+          <t>198066</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149902</t>
+          <t>152669</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>197320</t>
+          <t>201278</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>311577</t>
+          <t>310184</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>380429</t>
+          <t>374990</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>158201</t>
+          <t>159423</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>203399</t>
+          <t>204289</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>173928</t>
+          <t>174077</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>220913</t>
+          <t>225464</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>342954</t>
+          <t>343021</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>410118</t>
+          <t>409792</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>98431</t>
+          <t>97451</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138836</t>
+          <t>137587</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>124082</t>
+          <t>123555</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>167501</t>
+          <t>166281</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>232687</t>
+          <t>233169</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>291644</t>
+          <t>293568</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>106494</t>
+          <t>106449</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>145547</t>
+          <t>146571</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>129506</t>
+          <t>127098</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>172997</t>
+          <t>173843</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>246826</t>
+          <t>247228</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>304565</t>
+          <t>306090</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>83566</t>
+          <t>82899</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>119901</t>
+          <t>121760</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>124642</t>
+          <t>124363</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>166754</t>
+          <t>167922</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>219765</t>
+          <t>217560</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>276960</t>
+          <t>275666</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>67859</t>
+          <t>69957</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>102282</t>
+          <t>105014</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>76526</t>
+          <t>77715</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>116379</t>
+          <t>116031</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>156052</t>
+          <t>158402</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>206542</t>
+          <t>211911</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>39091</t>
+          <t>38999</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>64416</t>
+          <t>62943</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>273430</t>
+          <t>270205</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>329343</t>
+          <t>332061</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>316853</t>
+          <t>317297</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>384913</t>
+          <t>383213</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>24144</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>48313</t>
+          <t>47706</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>184484</t>
+          <t>184128</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>240184</t>
+          <t>237596</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>219079</t>
+          <t>213505</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>276317</t>
+          <t>273472</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>54261</t>
+          <t>55610</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>84310</t>
+          <t>85181</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>178710</t>
+          <t>176851</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>230258</t>
+          <t>228678</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>243350</t>
+          <t>243445</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>304655</t>
+          <t>304553</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>47748</t>
+          <t>47606</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>74616</t>
+          <t>76526</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,74 +4494,74 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>16,58%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>26,65%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>164867</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>143828</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>189877</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>15,38%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>13,41%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>226098</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>199912</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>257731</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
           <t>16,63%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>25,99%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>164867</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>141458</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>190580</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>15,38%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>17,78%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>226098</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>200001</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>256929</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
           <t>14,71%</t>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>58051</t>
+          <t>57443</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>87575</t>
+          <t>86831</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>170166</t>
+          <t>168882</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>224214</t>
+          <t>222359</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>235707</t>
+          <t>238747</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>297226</t>
+          <t>298053</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>775856</t>
+          <t>771577</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>872103</t>
+          <t>869120</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>780431</t>
+          <t>780988</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>888398</t>
+          <t>882685</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>1583433</t>
+          <t>1577944</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1727739</t>
+          <t>1729705</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>588740</t>
+          <t>588367</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>680113</t>
+          <t>682101</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>593105</t>
+          <t>586466</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>687970</t>
+          <t>688434</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1210621</t>
+          <t>1205403</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1338648</t>
+          <t>1339275</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>669225</t>
+          <t>677140</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>769346</t>
+          <t>773034</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>691730</t>
+          <t>692114</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>789695</t>
+          <t>795426</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1394234</t>
+          <t>1391898</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1537026</t>
+          <t>1532181</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>563612</t>
+          <t>562034</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>650953</t>
+          <t>650999</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>590375</t>
+          <t>587743</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>684407</t>
+          <t>682856</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1177607</t>
+          <t>1183134</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1312132</t>
+          <t>1307217</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>527093</t>
+          <t>530594</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>618967</t>
+          <t>617649</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>607269</t>
+          <t>608998</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>702516</t>
+          <t>703484</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1161044</t>
+          <t>1162585</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1289409</t>
+          <t>1293396</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
